--- a/dataset/config/antenna.xlsx
+++ b/dataset/config/antenna.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Kuliah-temp\Teknofest\program\dataset\config\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{307BE18D-2AD2-45E9-8C54-2E933DB7C15A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{03C3DFE2-9254-45A3-AD1B-8DE95F50A833}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{99887ECB-6D70-4376-A31A-BD0DC24DDF23}"/>
   </bookViews>
@@ -46,9 +46,6 @@
     <t xml:space="preserve">Sector </t>
   </si>
   <si>
-    <t xml:space="preserve">PCI </t>
-  </si>
-  <si>
     <t>rachroot</t>
   </si>
   <si>
@@ -143,6 +140,9 @@
   </si>
   <si>
     <t>`</t>
+  </si>
+  <si>
+    <t>PCI</t>
   </si>
 </sst>
 </file>
@@ -1049,51 +1049,51 @@
         <v>1</v>
       </c>
       <c r="C1" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="I1" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="J1" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="D1" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="E1" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="F1" s="2" t="s">
+      <c r="K1" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="L1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="M1" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="G1" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="H1" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="I1" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="J1" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="K1" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="L1" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="M1" s="2" t="s">
-        <v>28</v>
-      </c>
       <c r="N1" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="2" spans="1:14" ht="20.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="B2" s="10" t="s">
+      <c r="C2" s="10" t="s">
         <v>5</v>
-      </c>
-      <c r="C2" s="10" t="s">
-        <v>6</v>
       </c>
       <c r="D2" s="10">
         <v>41.107341300000002</v>
@@ -1114,7 +1114,7 @@
         <v>10</v>
       </c>
       <c r="J2" s="10" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="K2" s="10">
         <v>30</v>
@@ -1126,18 +1126,18 @@
         <v>200</v>
       </c>
       <c r="N2" s="11" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="3" spans="1:14" ht="20.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="5" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B3" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="C3" s="12" t="s">
         <v>8</v>
-      </c>
-      <c r="C3" s="12" t="s">
-        <v>9</v>
       </c>
       <c r="D3" s="12">
         <v>41.107087300000003</v>
@@ -1158,7 +1158,7 @@
         <v>10</v>
       </c>
       <c r="J3" s="12" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="K3" s="12">
         <v>40</v>
@@ -1170,18 +1170,18 @@
         <v>200</v>
       </c>
       <c r="N3" s="13" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="4" spans="1:14" ht="20.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="5" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B4" s="12" t="s">
+        <v>9</v>
+      </c>
+      <c r="C4" s="17" t="s">
         <v>10</v>
-      </c>
-      <c r="C4" s="17" t="s">
-        <v>11</v>
       </c>
       <c r="D4" s="17">
         <v>41.108086100000001</v>
@@ -1202,7 +1202,7 @@
         <v>6</v>
       </c>
       <c r="J4" s="17" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="K4" s="17">
         <v>59</v>
@@ -1214,18 +1214,18 @@
         <v>200</v>
       </c>
       <c r="N4" s="18" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="5" spans="1:14" ht="20.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="B5" s="14" t="s">
+        <v>4</v>
+      </c>
+      <c r="C5" s="17" t="s">
         <v>12</v>
-      </c>
-      <c r="B5" s="14" t="s">
-        <v>5</v>
-      </c>
-      <c r="C5" s="17" t="s">
-        <v>13</v>
       </c>
       <c r="D5" s="17">
         <v>41.108086100000001</v>
@@ -1246,7 +1246,7 @@
         <v>6</v>
       </c>
       <c r="J5" s="17" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="K5" s="17">
         <v>48</v>
@@ -1258,18 +1258,18 @@
         <v>200</v>
       </c>
       <c r="N5" s="18" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="6" spans="1:14" ht="20.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="7" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B6" s="14" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C6" s="19" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D6" s="19">
         <v>41.105469399999997</v>
@@ -1290,7 +1290,7 @@
         <v>18</v>
       </c>
       <c r="J6" s="19" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K6" s="19">
         <v>68</v>
@@ -1302,18 +1302,18 @@
         <v>200</v>
       </c>
       <c r="N6" s="20" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="7" spans="1:14" ht="20.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="7" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B7" s="14" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C7" s="19" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D7" s="19">
         <v>41.105469399999997</v>
@@ -1334,7 +1334,7 @@
         <v>18</v>
       </c>
       <c r="J7" s="19" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K7" s="19">
         <v>76</v>
@@ -1346,18 +1346,18 @@
         <v>200</v>
       </c>
       <c r="N7" s="20" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="8" spans="1:14" ht="20.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="B8" s="12" t="s">
+        <v>4</v>
+      </c>
+      <c r="C8" s="21" t="s">
         <v>16</v>
-      </c>
-      <c r="B8" s="12" t="s">
-        <v>5</v>
-      </c>
-      <c r="C8" s="21" t="s">
-        <v>17</v>
       </c>
       <c r="D8" s="21">
         <v>41.104341699999999</v>
@@ -1378,7 +1378,7 @@
         <v>6</v>
       </c>
       <c r="J8" s="21" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="K8" s="21">
         <v>3</v>
@@ -1390,18 +1390,18 @@
         <v>200</v>
       </c>
       <c r="N8" s="22" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="9" spans="1:14" ht="20.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B9" s="12" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C9" s="21" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D9" s="21">
         <v>41.104341699999999</v>
@@ -1422,7 +1422,7 @@
         <v>6</v>
       </c>
       <c r="J9" s="21" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="K9" s="21">
         <v>13</v>
@@ -1434,18 +1434,18 @@
         <v>200</v>
       </c>
       <c r="N9" s="22" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="10" spans="1:14" ht="20.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A10" s="6" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B10" s="15" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C10" s="15" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D10" s="15">
         <v>41.105841699999999</v>
@@ -1466,7 +1466,7 @@
         <v>6</v>
       </c>
       <c r="J10" s="15" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="K10" s="15">
         <v>23</v>
@@ -1478,12 +1478,12 @@
         <v>200</v>
       </c>
       <c r="N10" s="16" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="27" spans="8:8" ht="20.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="H27" s="9" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
   </sheetData>
@@ -1502,10 +1502,10 @@
   <sheetData>
     <row r="1" spans="1:12" ht="18" x14ac:dyDescent="0.35">
       <c r="A1" s="8" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="L1" s="8" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
   </sheetData>
